--- a/Runtime/PackageDefault/VNovelizerRes/ExcelVNScripts/Templates/ScriptTemplate.xlsx
+++ b/Runtime/PackageDefault/VNovelizerRes/ExcelVNScripts/Templates/ScriptTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity项目\VNovelizer\Assets\Resources\VNovelizerRes\ExcelVNScripts\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity项目\VNovelizer\Assets\Editor\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A3213F-4F40-4439-98E5-08BF96059982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A876BD64-4A0B-4830-ABBD-00E3D11150EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,14 +35,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>HeadProfile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CharLeft</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>CharMid_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CharMid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>CharMid_Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CharRight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -68,10 +80,6 @@
   </si>
   <si>
     <t>Note</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeadProfile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -400,19 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
-  <cols>
-    <col min="3" max="3" width="14.59765625" customWidth="1"/>
-    <col min="7" max="7" width="28.09765625" customWidth="1"/>
-    <col min="8" max="8" width="17.75" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="15.046875" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" customWidth="1"/>
-    <col min="12" max="12" width="21.6484375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,34 +419,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
